--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487517_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487517_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.3261</v>
+        <v>10.159</v>
       </c>
       <c r="E2" t="n">
-        <v>8.220599999999999</v>
+        <v>7.9466</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1055</v>
+        <v>2.2124</v>
       </c>
       <c r="G2" t="n">
         <v>5.4393</v>
@@ -610,13 +610,13 @@
         <v>2.9377</v>
       </c>
       <c r="S2" t="n">
-        <v>1.1035</v>
+        <v>0.9363</v>
       </c>
       <c r="T2" t="n">
-        <v>1.0722</v>
+        <v>0.7981</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0313</v>
+        <v>0.1382</v>
       </c>
       <c r="V2" t="n">
         <v>1.8249</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.4567</v>
+        <v>6.3696</v>
       </c>
       <c r="E3" t="n">
-        <v>4.9116</v>
+        <v>5.3969</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5451</v>
+        <v>0.9727</v>
       </c>
       <c r="G3" t="n">
         <v>0.3444</v>
@@ -688,13 +688,13 @@
         <v>2.1543</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4165</v>
+        <v>0.4964</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2923</v>
+        <v>0.1929</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1242</v>
+        <v>0.3035</v>
       </c>
       <c r="V3" t="n">
         <v>3.3745</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. ROQUE DO VALE CARVAHAL</t>
+          <t>D. SNYERS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.08</v>
+        <v>4.0205</v>
       </c>
       <c r="E4" t="n">
-        <v>3.7426</v>
+        <v>2.6198</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3374</v>
+        <v>1.4006</v>
       </c>
       <c r="G4" t="n">
-        <v>3.587</v>
+        <v>1.7163</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.4341</v>
+        <v>0.3233</v>
       </c>
       <c r="I4" t="n">
-        <v>4.0211</v>
+        <v>1.393</v>
       </c>
       <c r="J4" t="n">
-        <v>4.7942</v>
+        <v>1.9684</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3793</v>
+        <v>1.0003</v>
       </c>
       <c r="L4" t="n">
-        <v>4.4149</v>
+        <v>0.9681</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.2073</v>
+        <v>-0.2521</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.8135</v>
+        <v>-0.677</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.3938</v>
+        <v>0.4249</v>
       </c>
       <c r="P4" t="n">
-        <v>1.1751</v>
+        <v>1.3709</v>
       </c>
       <c r="Q4" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R4" t="n">
-        <v>2.1543</v>
+        <v>2.3502</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2016</v>
+        <v>0.2673</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0723</v>
+        <v>0.414</v>
       </c>
       <c r="U4" t="n">
-        <v>0.274</v>
+        <v>-0.1467</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.8837</v>
+        <v>0.6659</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.2166</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.8837</v>
+        <v>-0.5507</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. SNYERS</t>
+          <t>P. ROQUE DO VALE CARVAHAL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.7121</v>
+        <v>3.6232</v>
       </c>
       <c r="E5" t="n">
-        <v>2.1511</v>
+        <v>3.3927</v>
       </c>
       <c r="F5" t="n">
-        <v>1.561</v>
+        <v>0.2305</v>
       </c>
       <c r="G5" t="n">
-        <v>1.7163</v>
+        <v>3.587</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3233</v>
+        <v>-0.4341</v>
       </c>
       <c r="I5" t="n">
-        <v>1.393</v>
+        <v>4.0211</v>
       </c>
       <c r="J5" t="n">
-        <v>1.9684</v>
+        <v>4.7942</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0003</v>
+        <v>0.3793</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9681</v>
+        <v>4.4149</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2521</v>
+        <v>-1.2073</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.677</v>
+        <v>-0.8135</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4249</v>
+        <v>-0.3938</v>
       </c>
       <c r="P5" t="n">
-        <v>1.3709</v>
+        <v>1.1751</v>
       </c>
       <c r="Q5" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R5" t="n">
-        <v>2.3502</v>
+        <v>2.1543</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.041</v>
+        <v>-0.2553</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0547</v>
+        <v>-0.4223</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0137</v>
+        <v>0.167</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6659</v>
+        <v>-0.8837</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2166</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5507</v>
+        <v>-0.8837</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G. SABATER MARTINEZ</t>
+          <t>M. GARCIA FRAGA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.4538</v>
+        <v>3.3563</v>
       </c>
       <c r="E6" t="n">
-        <v>0.952</v>
+        <v>2.2777</v>
       </c>
       <c r="F6" t="n">
-        <v>2.5017</v>
+        <v>1.0785</v>
       </c>
       <c r="G6" t="n">
-        <v>0.74</v>
+        <v>0.8758</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.1239</v>
+        <v>-0.6856</v>
       </c>
       <c r="I6" t="n">
-        <v>1.8639</v>
+        <v>1.5614</v>
       </c>
       <c r="J6" t="n">
-        <v>1.939</v>
+        <v>1.4758</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5052</v>
+        <v>0.0612</v>
       </c>
       <c r="L6" t="n">
-        <v>1.4338</v>
+        <v>1.4145</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.1989</v>
+        <v>-0.6</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.629</v>
+        <v>-0.7468</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4301</v>
+        <v>0.1468</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7834</v>
+        <v>1.5668</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.9585</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.7419</v>
+        <v>1.5668</v>
       </c>
       <c r="S6" t="n">
-        <v>2.3208</v>
+        <v>-0.9688</v>
       </c>
       <c r="T6" t="n">
-        <v>1.695</v>
+        <v>-0.4146</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6258</v>
+        <v>-0.5542</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.3905</v>
+        <v>1.8825</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.7235</v>
+        <v>1.2166</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3329</v>
+        <v>0.6659</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. GARCIA FRAGA</t>
+          <t>A. IGLESIAS FERNANDEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.9539</v>
+        <v>2.2777</v>
       </c>
       <c r="E7" t="n">
-        <v>2.116</v>
+        <v>0.7127</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8379</v>
+        <v>1.565</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8758</v>
+        <v>1.068</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6856</v>
+        <v>-1.068</v>
       </c>
       <c r="I7" t="n">
-        <v>1.5614</v>
+        <v>2.1361</v>
       </c>
       <c r="J7" t="n">
-        <v>1.4758</v>
+        <v>2.2065</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0612</v>
+        <v>0.3589</v>
       </c>
       <c r="L7" t="n">
-        <v>1.4145</v>
+        <v>1.8476</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.6</v>
+        <v>-1.1385</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7468</v>
+        <v>-1.427</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1468</v>
+        <v>0.2885</v>
       </c>
       <c r="P7" t="n">
-        <v>1.5668</v>
+        <v>0.5875</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.9585</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5668</v>
+        <v>2.546</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.3711</v>
+        <v>0.2316</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5764</v>
+        <v>0.4646</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.7947</v>
+        <v>-0.233</v>
       </c>
       <c r="V7" t="n">
-        <v>1.8825</v>
+        <v>0.3905</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2166</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6659</v>
+        <v>0.3905</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. IGLESIAS FERNANDEZ</t>
+          <t>G. SABATER MARTINEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.4296</v>
+        <v>1.8321</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4295</v>
+        <v>-0.0549</v>
       </c>
       <c r="F8" t="n">
-        <v>1.8591</v>
+        <v>1.8869</v>
       </c>
       <c r="G8" t="n">
-        <v>1.068</v>
+        <v>0.74</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.068</v>
+        <v>-1.1239</v>
       </c>
       <c r="I8" t="n">
-        <v>2.1361</v>
+        <v>1.8639</v>
       </c>
       <c r="J8" t="n">
-        <v>2.2065</v>
+        <v>1.939</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3589</v>
+        <v>0.5052</v>
       </c>
       <c r="L8" t="n">
-        <v>1.8476</v>
+        <v>1.4338</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.1385</v>
+        <v>-1.1989</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.427</v>
+        <v>-1.629</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2885</v>
+        <v>0.4301</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5875</v>
+        <v>0.7834</v>
       </c>
       <c r="Q8" t="n">
         <v>-1.9585</v>
       </c>
       <c r="R8" t="n">
-        <v>2.546</v>
+        <v>2.7419</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6165</v>
+        <v>0.6991000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6775</v>
+        <v>0.6881</v>
       </c>
       <c r="U8" t="n">
-        <v>0.061</v>
+        <v>0.011</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3905</v>
+        <v>-0.3905</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-0.7235</v>
       </c>
       <c r="X8" t="n">
-        <v>0.3905</v>
+        <v>0.3329</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>I. LUACES PENIN</t>
+          <t>S. YUBERO ROSALES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.1572</v>
+        <v>1.4062</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.5709</v>
+        <v>1.1574</v>
       </c>
       <c r="F9" t="n">
-        <v>1.7281</v>
+        <v>0.2488</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7243000000000001</v>
+        <v>1.0607</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4158</v>
+        <v>0.0752</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3085</v>
+        <v>0.9855</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4389</v>
+        <v>1.6555</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2773</v>
+        <v>0.6856</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1617</v>
+        <v>0.97</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2854</v>
+        <v>-0.5948</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1385</v>
+        <v>-0.6104000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1468</v>
+        <v>0.0156</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5875</v>
+        <v>2.3502</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5668</v>
+        <v>2.3502</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1546</v>
+        <v>0.2107</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0306</v>
+        <v>-0.1076</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.124</v>
+        <v>0.3183</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-2.2154</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-0.3905</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.8249</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. YUBERO ROSALES</t>
+          <t>I. LUACES PENIN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7979000000000001</v>
+        <v>0.9944</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6292</v>
+        <v>-0.9208</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1686</v>
+        <v>1.9152</v>
       </c>
       <c r="G10" t="n">
-        <v>1.0607</v>
+        <v>0.7243000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0752</v>
+        <v>0.4158</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9855</v>
+        <v>0.3085</v>
       </c>
       <c r="J10" t="n">
-        <v>1.6555</v>
+        <v>0.4389</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6856</v>
+        <v>0.2773</v>
       </c>
       <c r="L10" t="n">
-        <v>0.97</v>
+        <v>0.1617</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.5948</v>
+        <v>0.2854</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6104000000000001</v>
+        <v>0.1385</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0156</v>
+        <v>0.1468</v>
       </c>
       <c r="P10" t="n">
-        <v>2.3502</v>
+        <v>0.5875</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R10" t="n">
-        <v>2.3502</v>
+        <v>1.5668</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3976</v>
+        <v>-0.3174</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6358</v>
+        <v>-0.3805</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2381</v>
+        <v>0.0631</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.2154</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.3905</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.8249</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.293</v>
+        <v>-0.2663</v>
       </c>
       <c r="E11" t="n">
         <v>-0.0984</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1946</v>
+        <v>-0.1679</v>
       </c>
       <c r="G11" t="n">
         <v>-0.2514</v>
@@ -1312,13 +1312,13 @@
         <v>0.1958</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2374</v>
+        <v>-0.2107</v>
       </c>
       <c r="T11" t="n">
         <v>-0.1188</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1186</v>
+        <v>-0.0919</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.8506</v>
+        <v>-2.3608</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.5278</v>
+        <v>-2.145</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.3228</v>
+        <v>-0.2158</v>
       </c>
       <c r="G12" t="n">
         <v>-2.6793</v>
@@ -1390,13 +1390,13 @@
         <v>1.9585</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5998</v>
+        <v>-0.11</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5587</v>
+        <v>-0.1759</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.041</v>
+        <v>0.0659</v>
       </c>
       <c r="V12" t="n">
         <v>-0.5507</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>30.2237</v>
+        <v>31.4119</v>
       </c>
       <c r="E13" t="n">
-        <v>19.0965</v>
+        <v>20.2847</v>
       </c>
       <c r="F13" t="n">
-        <v>11.127</v>
+        <v>11.1269</v>
       </c>
       <c r="G13" t="n">
         <v>12.6251</v>
@@ -1456,25 +1456,25 @@
         <v>-10.52</v>
       </c>
       <c r="O13" t="n">
-        <v>0.8377999999999999</v>
+        <v>0.8378</v>
       </c>
       <c r="P13" t="n">
         <v>13.7092</v>
       </c>
       <c r="Q13" t="n">
-        <v>-8.813000000000001</v>
+        <v>-8.812999999999999</v>
       </c>
       <c r="R13" t="n">
         <v>22.5225</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2085999999999997</v>
+        <v>0.9792</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2498999999999999</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>0.04140000000000007</v>
+        <v>0.0412</v>
       </c>
       <c r="V13" t="n">
         <v>4.098000000000001</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.7938</v>
+        <v>5.7154</v>
       </c>
       <c r="E14" t="n">
-        <v>6.6067</v>
+        <v>6.095</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.8129</v>
+        <v>-0.3797</v>
       </c>
       <c r="G14" t="n">
         <v>4.6342</v>
@@ -1546,13 +1546,13 @@
         <v>1.5668</v>
       </c>
       <c r="S14" t="n">
-        <v>1.2932</v>
+        <v>1.2148</v>
       </c>
       <c r="T14" t="n">
-        <v>0.9357</v>
+        <v>0.424</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3575</v>
+        <v>0.7907999999999999</v>
       </c>
       <c r="V14" t="n">
         <v>1.8249</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.3276</v>
+        <v>1.8633</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3224</v>
+        <v>0.4247</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0052</v>
+        <v>1.4385</v>
       </c>
       <c r="G15" t="n">
         <v>1.7665</v>
@@ -1624,13 +1624,13 @@
         <v>0.9792</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.243</v>
+        <v>0.2926</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1059</v>
+        <v>0.2082</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3489</v>
+        <v>0.0844</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2805</v>
+        <v>0.463</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0218</v>
+        <v>0.1242</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2587</v>
+        <v>0.3388</v>
       </c>
       <c r="G16" t="n">
         <v>0.2864</v>
@@ -1702,13 +1702,13 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0059</v>
+        <v>0.1766</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0594</v>
+        <v>0.0429</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0535</v>
+        <v>0.1337</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0828</v>
+        <v>-0.1818</v>
       </c>
       <c r="E17" t="n">
         <v>1.3698</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.2871</v>
+        <v>-1.5516</v>
       </c>
       <c r="G17" t="n">
         <v>3.823</v>
@@ -1780,13 +1780,13 @@
         <v>0.9792</v>
       </c>
       <c r="S17" t="n">
-        <v>0.7665999999999999</v>
+        <v>0.5021</v>
       </c>
       <c r="T17" t="n">
         <v>0.0288</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7378</v>
+        <v>0.4733</v>
       </c>
       <c r="V17" t="n">
         <v>-2.5484</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.2932</v>
+        <v>-1.4251</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.7282999999999999</v>
+        <v>-1.24</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5649</v>
+        <v>-0.1851</v>
       </c>
       <c r="G18" t="n">
         <v>-0.5368000000000001</v>
@@ -1858,13 +1858,13 @@
         <v>1.3709</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3795</v>
+        <v>0.2476</v>
       </c>
       <c r="T18" t="n">
-        <v>0.7993</v>
+        <v>0.2876</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4198</v>
+        <v>-0.04</v>
       </c>
       <c r="V18" t="n">
         <v>-1.3318</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.3624</v>
+        <v>-2.8758</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.2715</v>
+        <v>-0.6808</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.0909</v>
+        <v>-2.195</v>
       </c>
       <c r="G19" t="n">
         <v>-2.7187</v>
@@ -1936,13 +1936,13 @@
         <v>0.3917</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7065</v>
+        <v>0.1931</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0306</v>
+        <v>-0.4399</v>
       </c>
       <c r="U19" t="n">
-        <v>0.7371</v>
+        <v>0.633</v>
       </c>
       <c r="V19" t="n">
         <v>1.2166</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.5263</v>
+        <v>-3.8957</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.8129</v>
+        <v>-2.5059</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.7134</v>
+        <v>-1.3898</v>
       </c>
       <c r="G20" t="n">
         <v>-2.2814</v>
@@ -2014,13 +2014,13 @@
         <v>0.1958</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.1274</v>
+        <v>-0.4968</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.22</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.9074</v>
+        <v>-0.5839</v>
       </c>
       <c r="V20" t="n">
         <v>0.0576</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.9346</v>
+        <v>-4.6174</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.7886</v>
+        <v>-3.5839</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.146</v>
+        <v>-1.0335</v>
       </c>
       <c r="G21" t="n">
         <v>-4.0483</v>
@@ -2092,13 +2092,13 @@
         <v>0.7834</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0234</v>
+        <v>0.2938</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5652</v>
+        <v>-0.3605</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5417999999999999</v>
+        <v>0.6543</v>
       </c>
       <c r="V21" t="n">
         <v>-0.2754</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.0727</v>
+        <v>-4.9315</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.0296</v>
+        <v>-1.7226</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.0431</v>
+        <v>-3.2089</v>
       </c>
       <c r="G22" t="n">
         <v>-3.771</v>
@@ -2170,13 +2170,13 @@
         <v>1.3709</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0691</v>
+        <v>0.0722</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5476</v>
+        <v>-0.2406</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5215</v>
+        <v>0.3127</v>
       </c>
       <c r="V22" t="n">
         <v>-0.0576</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.3146</v>
+        <v>-6.4676</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.0783</v>
+        <v>-4.1806</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.2363</v>
+        <v>-2.287</v>
       </c>
       <c r="G23" t="n">
         <v>-4.5714</v>
@@ -2248,13 +2248,13 @@
         <v>0.5875</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0589</v>
+        <v>-0.2119</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1476</v>
+        <v>0.0453</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2065</v>
+        <v>-0.2572</v>
       </c>
       <c r="V23" t="n">
         <v>0.6659</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-12.2046</v>
+        <v>-11.8237</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.7386</v>
+        <v>-5.227</v>
       </c>
       <c r="F24" t="n">
-        <v>-6.4659</v>
+        <v>-6.5968</v>
       </c>
       <c r="G24" t="n">
         <v>-5.2077</v>
@@ -2326,13 +2326,13 @@
         <v>0.5875</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.4093</v>
+        <v>-0.0285</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6358</v>
+        <v>-0.1241</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2264</v>
+        <v>0.0956</v>
       </c>
       <c r="V24" t="n">
         <v>-3.6498</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-30.2237</v>
+        <v>-28.1769</v>
       </c>
       <c r="E25" t="n">
         <v>-11.1271</v>
       </c>
       <c r="F25" t="n">
-        <v>-19.0966</v>
+        <v>-17.0501</v>
       </c>
       <c r="G25" t="n">
         <v>-12.6252</v>
@@ -2404,13 +2404,13 @@
         <v>8.812899999999999</v>
       </c>
       <c r="S25" t="n">
-        <v>0.2087999999999999</v>
+        <v>2.2556</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.0413</v>
+        <v>-0.04129999999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>0.2500000000000001</v>
+        <v>2.2967</v>
       </c>
       <c r="V25" t="n">
         <v>-4.098</v>
